--- a/data/all_data_df.xlsx
+++ b/data/all_data_df.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ157"/>
+  <dimension ref="A1:AQ157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -609,6 +609,41 @@
           <t>num_funded_teams</t>
         </is>
       </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>num_teams_numeric</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>num_funded_teams_numeric</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>meeting_length_numeric</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>percent_time_screenshare_numeric</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>num_members_numeric</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>has_teams</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>has_funded_teams</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -723,6 +758,27 @@
       <c r="AJ2" t="n">
         <v>0</v>
       </c>
+      <c r="AK2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>770</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>9</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -837,6 +893,27 @@
       <c r="AJ3" t="n">
         <v>1</v>
       </c>
+      <c r="AK3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1819</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -951,6 +1028,27 @@
       <c r="AJ4" t="n">
         <v>0</v>
       </c>
+      <c r="AK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>2236</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>100</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>11</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -982,7 +1080,7 @@
         <v>30</v>
       </c>
       <c r="I5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J5" t="n">
         <v>8</v>
@@ -1063,6 +1161,27 @@
         <v>2</v>
       </c>
       <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1795</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>12</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1179,6 +1298,27 @@
       <c r="AJ6" t="n">
         <v>0</v>
       </c>
+      <c r="AK6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>2165</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>13</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1293,6 +1433,27 @@
       <c r="AJ7" t="n">
         <v>1</v>
       </c>
+      <c r="AK7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>2313</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>69.95244271508862</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1407,6 +1568,27 @@
       <c r="AJ8" t="n">
         <v>1</v>
       </c>
+      <c r="AK8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>2890</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1521,6 +1703,27 @@
       <c r="AJ9" t="n">
         <v>2</v>
       </c>
+      <c r="AK9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>2836</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>98.58956276445699</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>17</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1635,6 +1838,27 @@
       <c r="AJ10" t="n">
         <v>0</v>
       </c>
+      <c r="AK10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1835</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>11</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1749,6 +1973,27 @@
       <c r="AJ11" t="n">
         <v>1</v>
       </c>
+      <c r="AK11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1619</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>15.75046324891909</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1863,6 +2108,27 @@
       <c r="AJ12" t="n">
         <v>0</v>
       </c>
+      <c r="AK12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1637</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>12.82834453268173</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>14</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1977,6 +2243,27 @@
       <c r="AJ13" t="n">
         <v>0</v>
       </c>
+      <c r="AK13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>2321</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>9.43558810857389</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>13</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2091,6 +2378,27 @@
       <c r="AJ14" t="n">
         <v>1</v>
       </c>
+      <c r="AK14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1084</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>9</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2205,6 +2513,27 @@
       <c r="AJ15" t="n">
         <v>2</v>
       </c>
+      <c r="AK15" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>790</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>21.64556962025316</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>14</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2319,6 +2648,27 @@
       <c r="AJ16" t="n">
         <v>0</v>
       </c>
+      <c r="AK16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1873</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>39.1350774159103</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2433,6 +2783,27 @@
       <c r="AJ17" t="n">
         <v>1</v>
       </c>
+      <c r="AK17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>606</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>100</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>12</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2464,7 +2835,7 @@
         <v>44</v>
       </c>
       <c r="I18" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J18" t="n">
         <v>21</v>
@@ -2491,7 +2862,7 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2506,7 +2877,7 @@
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X18" t="n">
         <v>8</v>
@@ -2545,6 +2916,27 @@
         <v>2</v>
       </c>
       <c r="AJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>4067</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>11.33513646422424</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>13</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2581,7 +2973,7 @@
         <v>54</v>
       </c>
       <c r="J19" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K19" t="n">
         <v>29</v>
@@ -2659,6 +3051,27 @@
         <v>1</v>
       </c>
       <c r="AJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>3347</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>15.62593367194502</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>11</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2689,7 +3102,7 @@
         <v>17</v>
       </c>
       <c r="H20" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I20" t="n">
         <v>27</v>
@@ -2773,6 +3186,27 @@
         <v>1</v>
       </c>
       <c r="AJ20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>3649</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>21.89640997533571</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>20</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ20" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2833,7 +3267,7 @@
         <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="S21" t="n">
         <v>24</v>
@@ -2887,6 +3321,27 @@
         <v>0</v>
       </c>
       <c r="AJ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>2949</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>26.34791454730417</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>19</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2902,7 +3357,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D22" t="n">
         <v>3513</v>
@@ -2917,22 +3372,22 @@
         <v>22</v>
       </c>
       <c r="H22" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I22" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J22" t="n">
         <v>16</v>
       </c>
       <c r="K22" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L22" t="n">
         <v>18</v>
       </c>
       <c r="M22" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N22" t="n">
         <v>1</v>
@@ -3001,6 +3456,27 @@
         <v>0</v>
       </c>
       <c r="AJ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>3513</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>21.94705380017079</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>14</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3016,7 +3492,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D23" t="n">
         <v>3230</v>
@@ -3115,6 +3591,27 @@
         <v>2</v>
       </c>
       <c r="AJ23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>3230</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>12</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ23" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3130,7 +3627,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D24" t="n">
         <v>3172</v>
@@ -3230,6 +3727,27 @@
       </c>
       <c r="AJ24" t="n">
         <v>2</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>3172</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>8.764186633039092</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>15</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -3259,7 +3777,7 @@
         <v>15</v>
       </c>
       <c r="H25" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I25" t="n">
         <v>50</v>
@@ -3283,7 +3801,7 @@
         <v>10</v>
       </c>
       <c r="P25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q25" t="n">
         <v>7</v>
@@ -3343,6 +3861,27 @@
         <v>0</v>
       </c>
       <c r="AJ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>3371</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>7.475526549985167</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>14</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3376,16 +3915,16 @@
         <v>52</v>
       </c>
       <c r="I26" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J26" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K26" t="n">
         <v>8</v>
       </c>
       <c r="L26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M26" t="n">
         <v>31</v>
@@ -3457,6 +3996,27 @@
         <v>1</v>
       </c>
       <c r="AJ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>2749</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>9.3488541287741</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>44</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3472,7 +4032,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D27" t="n">
         <v>3297</v>
@@ -3490,7 +4050,7 @@
         <v>48</v>
       </c>
       <c r="I27" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J27" t="n">
         <v>20</v>
@@ -3571,6 +4131,27 @@
         <v>1</v>
       </c>
       <c r="AJ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>3297</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>7.825295723384896</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>12</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3586,7 +4167,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D28" t="n">
         <v>3033</v>
@@ -3604,7 +4185,7 @@
         <v>43</v>
       </c>
       <c r="I28" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J28" t="n">
         <v>14</v>
@@ -3634,7 +4215,7 @@
         <v>27</v>
       </c>
       <c r="S28" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="T28" t="n">
         <v>2</v>
@@ -3670,7 +4251,7 @@
         <v>4</v>
       </c>
       <c r="AE28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF28" t="n">
         <v>1</v>
@@ -3685,6 +4266,27 @@
         <v>0</v>
       </c>
       <c r="AJ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>3033</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3718,7 +4320,7 @@
         <v>41</v>
       </c>
       <c r="I29" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J29" t="n">
         <v>9</v>
@@ -3727,7 +4329,7 @@
         <v>28</v>
       </c>
       <c r="L29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M29" t="n">
         <v>29</v>
@@ -3748,7 +4350,7 @@
         <v>21</v>
       </c>
       <c r="S29" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="T29" t="n">
         <v>1</v>
@@ -3784,7 +4386,7 @@
         <v>9</v>
       </c>
       <c r="AE29" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF29" t="n">
         <v>1</v>
@@ -3799,6 +4401,27 @@
         <v>2</v>
       </c>
       <c r="AJ29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>3441</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>6.480674222609705</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>17</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ29" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3915,6 +4538,27 @@
       <c r="AJ30" t="n">
         <v>0</v>
       </c>
+      <c r="AK30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>3579</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>3.93964794635373</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>12</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3928,7 +4572,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D31" t="n">
         <v>3694</v>
@@ -3973,7 +4617,7 @@
         <v>3</v>
       </c>
       <c r="R31" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="S31" t="n">
         <v>18</v>
@@ -4027,6 +4671,27 @@
         <v>1</v>
       </c>
       <c r="AJ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>3694</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>5.224688684353005</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4060,7 +4725,7 @@
         <v>62</v>
       </c>
       <c r="I32" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J32" t="n">
         <v>23</v>
@@ -4090,7 +4755,7 @@
         <v>13</v>
       </c>
       <c r="S32" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="T32" t="n">
         <v>4</v>
@@ -4126,7 +4791,7 @@
         <v>6</v>
       </c>
       <c r="AE32" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF32" t="n">
         <v>1</v>
@@ -4141,6 +4806,27 @@
         <v>3</v>
       </c>
       <c r="AJ32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>4227</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>5.086349656967116</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>20</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ32" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4183,7 +4869,7 @@
         <v>18</v>
       </c>
       <c r="L33" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M33" t="n">
         <v>32</v>
@@ -4255,6 +4941,27 @@
         <v>3</v>
       </c>
       <c r="AJ33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>3480</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>0.9195402298850575</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>13</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ33" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4371,6 +5078,27 @@
       <c r="AJ34" t="n">
         <v>1</v>
       </c>
+      <c r="AK34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>3755</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>4.607190412782956</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>15</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -4384,7 +5112,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D35" t="n">
         <v>3687</v>
@@ -4402,7 +5130,7 @@
         <v>57</v>
       </c>
       <c r="I35" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J35" t="n">
         <v>20</v>
@@ -4483,6 +5211,27 @@
         <v>0</v>
       </c>
       <c r="AJ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>3687</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>5.804176837537294</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>14</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ35" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4498,7 +5247,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D36" t="n">
         <v>3427</v>
@@ -4597,6 +5346,27 @@
         <v>3</v>
       </c>
       <c r="AJ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>3427</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>16.10738255033557</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>18</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ36" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4612,7 +5382,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D37" t="n">
         <v>3237</v>
@@ -4711,6 +5481,27 @@
         <v>2</v>
       </c>
       <c r="AJ37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>3237</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>0.09267840593141798</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>12</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ37" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4726,7 +5517,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D38" t="n">
         <v>4107</v>
@@ -4756,7 +5547,7 @@
         <v>17</v>
       </c>
       <c r="M38" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="N38" t="n">
         <v>13</v>
@@ -4825,6 +5616,27 @@
         <v>2</v>
       </c>
       <c r="AJ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>4107</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>7.523739956172388</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>13</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ38" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4840,7 +5652,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D39" t="n">
         <v>2959</v>
@@ -4855,7 +5667,7 @@
         <v>11</v>
       </c>
       <c r="H39" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I39" t="n">
         <v>27</v>
@@ -4939,6 +5751,27 @@
         <v>3</v>
       </c>
       <c r="AJ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>2959</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>15.91753970936127</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>15</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ39" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5055,6 +5888,27 @@
       <c r="AJ40" t="n">
         <v>0</v>
       </c>
+      <c r="AK40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>2042</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>96.42507345739472</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>12</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -5068,7 +5922,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D41" t="n">
         <v>3932</v>
@@ -5083,7 +5937,7 @@
         <v>8</v>
       </c>
       <c r="H41" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I41" t="n">
         <v>32</v>
@@ -5167,6 +6021,27 @@
         <v>2</v>
       </c>
       <c r="AJ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>3932</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>6.637843336724314</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>13</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ41" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5227,10 +6102,10 @@
         <v>3</v>
       </c>
       <c r="R42" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="S42" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="T42" t="n">
         <v>0</v>
@@ -5281,6 +6156,27 @@
         <v>1</v>
       </c>
       <c r="AJ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>3511</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>6.493876388493307</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>11</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ42" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5397,6 +6293,27 @@
       <c r="AJ43" t="n">
         <v>0</v>
       </c>
+      <c r="AK43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ43" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -5511,6 +6428,27 @@
       <c r="AJ44" t="n">
         <v>0</v>
       </c>
+      <c r="AK44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM44" t="n">
+        <v>3247</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>2.925777640899291</v>
+      </c>
+      <c r="AO44" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ44" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -5625,6 +6563,27 @@
       <c r="AJ45" t="n">
         <v>0</v>
       </c>
+      <c r="AK45" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM45" t="n">
+        <v>3107</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>22.65851303508207</v>
+      </c>
+      <c r="AO45" t="n">
+        <v>13</v>
+      </c>
+      <c r="AP45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ45" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -5638,7 +6597,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D46" t="n">
         <v>3152</v>
@@ -5656,7 +6615,7 @@
         <v>40</v>
       </c>
       <c r="I46" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J46" t="n">
         <v>12</v>
@@ -5686,7 +6645,7 @@
         <v>14</v>
       </c>
       <c r="S46" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T46" t="n">
         <v>3</v>
@@ -5722,7 +6681,7 @@
         <v>11</v>
       </c>
       <c r="AE46" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AF46" t="n">
         <v>2</v>
@@ -5737,6 +6696,27 @@
         <v>2</v>
       </c>
       <c r="AJ46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK46" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM46" t="n">
+        <v>3152</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>0.983502538071066</v>
+      </c>
+      <c r="AO46" t="n">
+        <v>35</v>
+      </c>
+      <c r="AP46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ46" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5853,6 +6833,27 @@
       <c r="AJ47" t="n">
         <v>1</v>
       </c>
+      <c r="AK47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM47" t="n">
+        <v>3396</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>23.55712603062426</v>
+      </c>
+      <c r="AO47" t="n">
+        <v>16</v>
+      </c>
+      <c r="AP47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ47" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -5866,7 +6867,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D48" t="n">
         <v>3013</v>
@@ -5884,7 +6885,7 @@
         <v>45</v>
       </c>
       <c r="I48" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J48" t="n">
         <v>15</v>
@@ -5965,6 +6966,27 @@
         <v>2</v>
       </c>
       <c r="AJ48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK48" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM48" t="n">
+        <v>3013</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>96.84699634915367</v>
+      </c>
+      <c r="AO48" t="n">
+        <v>13</v>
+      </c>
+      <c r="AP48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ48" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6007,7 +7029,7 @@
         <v>17</v>
       </c>
       <c r="L49" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M49" t="n">
         <v>22</v>
@@ -6079,6 +7101,27 @@
         <v>3</v>
       </c>
       <c r="AJ49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK49" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM49" t="n">
+        <v>3107</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>7.080785323463147</v>
+      </c>
+      <c r="AO49" t="n">
+        <v>9</v>
+      </c>
+      <c r="AP49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ49" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6127,7 +7170,7 @@
         <v>32</v>
       </c>
       <c r="N50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O50" t="n">
         <v>11</v>
@@ -6163,7 +7206,7 @@
         <v>9</v>
       </c>
       <c r="Z50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA50" t="n">
         <v>4</v>
@@ -6193,6 +7236,27 @@
         <v>1</v>
       </c>
       <c r="AJ50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM50" t="n">
+        <v>3445</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO50" t="n">
+        <v>11</v>
+      </c>
+      <c r="AP50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ50" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6232,7 +7296,7 @@
         <v>20</v>
       </c>
       <c r="K51" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L51" t="n">
         <v>7</v>
@@ -6253,7 +7317,7 @@
         <v>5</v>
       </c>
       <c r="R51" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S51" t="n">
         <v>27</v>
@@ -6307,6 +7371,27 @@
         <v>0</v>
       </c>
       <c r="AJ51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM51" t="n">
+        <v>3256</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>10.07371007371007</v>
+      </c>
+      <c r="AO51" t="n">
+        <v>16</v>
+      </c>
+      <c r="AP51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ51" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6352,7 +7437,7 @@
         <v>15</v>
       </c>
       <c r="M52" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N52" t="n">
         <v>3</v>
@@ -6361,7 +7446,7 @@
         <v>3</v>
       </c>
       <c r="P52" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q52" t="n">
         <v>8</v>
@@ -6397,7 +7482,7 @@
         <v>3</v>
       </c>
       <c r="AB52" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC52" t="n">
         <v>7</v>
@@ -6421,6 +7506,27 @@
         <v>0</v>
       </c>
       <c r="AJ52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM52" t="n">
+        <v>3815</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>72.11009174311927</v>
+      </c>
+      <c r="AO52" t="n">
+        <v>57</v>
+      </c>
+      <c r="AP52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ52" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6454,7 +7560,7 @@
         <v>45</v>
       </c>
       <c r="I53" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J53" t="n">
         <v>21</v>
@@ -6466,13 +7572,13 @@
         <v>14</v>
       </c>
       <c r="M53" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N53" t="n">
         <v>6</v>
       </c>
       <c r="O53" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P53" t="n">
         <v>4</v>
@@ -6535,6 +7641,27 @@
         <v>0</v>
       </c>
       <c r="AJ53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM53" t="n">
+        <v>3862</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>13.01139306059037</v>
+      </c>
+      <c r="AO53" t="n">
+        <v>16</v>
+      </c>
+      <c r="AP53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ53" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6598,7 +7725,7 @@
         <v>17</v>
       </c>
       <c r="S54" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="T54" t="n">
         <v>3</v>
@@ -6649,6 +7776,27 @@
         <v>0</v>
       </c>
       <c r="AJ54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM54" t="n">
+        <v>3163</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>17.07239962061334</v>
+      </c>
+      <c r="AO54" t="n">
+        <v>14</v>
+      </c>
+      <c r="AP54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ54" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6682,7 +7830,7 @@
         <v>32</v>
       </c>
       <c r="I55" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J55" t="n">
         <v>14</v>
@@ -6763,6 +7911,27 @@
         <v>2</v>
       </c>
       <c r="AJ55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK55" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM55" t="n">
+        <v>2663</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>0.6383777694329703</v>
+      </c>
+      <c r="AO55" t="n">
+        <v>13</v>
+      </c>
+      <c r="AP55" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ55" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6799,7 +7968,7 @@
         <v>22</v>
       </c>
       <c r="J56" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K56" t="n">
         <v>4</v>
@@ -6877,6 +8046,27 @@
         <v>2</v>
       </c>
       <c r="AJ56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK56" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM56" t="n">
+        <v>2953</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>14.69691838807992</v>
+      </c>
+      <c r="AO56" t="n">
+        <v>16</v>
+      </c>
+      <c r="AP56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ56" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6910,7 +8100,7 @@
         <v>52</v>
       </c>
       <c r="I57" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J57" t="n">
         <v>25</v>
@@ -6991,6 +8181,27 @@
         <v>1</v>
       </c>
       <c r="AJ57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM57" t="n">
+        <v>3727</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO57" t="n">
+        <v>11</v>
+      </c>
+      <c r="AP57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ57" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7107,6 +8318,27 @@
       <c r="AJ58" t="n">
         <v>0</v>
       </c>
+      <c r="AK58" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM58" t="n">
+        <v>3576</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>38.53467561521253</v>
+      </c>
+      <c r="AO58" t="n">
+        <v>12</v>
+      </c>
+      <c r="AP58" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ58" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -7135,10 +8367,10 @@
         <v>8</v>
       </c>
       <c r="H59" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I59" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J59" t="n">
         <v>15</v>
@@ -7150,7 +8382,7 @@
         <v>22</v>
       </c>
       <c r="M59" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N59" t="n">
         <v>1</v>
@@ -7219,6 +8451,27 @@
         <v>0</v>
       </c>
       <c r="AJ59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM59" t="n">
+        <v>3059</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>21.96796338672769</v>
+      </c>
+      <c r="AO59" t="n">
+        <v>19</v>
+      </c>
+      <c r="AP59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ59" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7252,7 +8505,7 @@
         <v>47</v>
       </c>
       <c r="I60" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J60" t="n">
         <v>15</v>
@@ -7279,7 +8532,7 @@
         <v>3</v>
       </c>
       <c r="R60" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="S60" t="n">
         <v>30</v>
@@ -7333,6 +8586,27 @@
         <v>2</v>
       </c>
       <c r="AJ60" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK60" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL60" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM60" t="n">
+        <v>3168</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>8.270202020202021</v>
+      </c>
+      <c r="AO60" t="n">
+        <v>14</v>
+      </c>
+      <c r="AP60" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ60" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7363,7 +8637,7 @@
         <v>18</v>
       </c>
       <c r="H61" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I61" t="n">
         <v>52</v>
@@ -7447,6 +8721,27 @@
         <v>2</v>
       </c>
       <c r="AJ61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK61" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM61" t="n">
+        <v>3534</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>8.970005659309564</v>
+      </c>
+      <c r="AO61" t="n">
+        <v>12</v>
+      </c>
+      <c r="AP61" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ61" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7563,6 +8858,27 @@
       <c r="AJ62" t="n">
         <v>0</v>
       </c>
+      <c r="AK62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM62" t="n">
+        <v>3449</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>2.290518991011888</v>
+      </c>
+      <c r="AO62" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ62" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -7591,10 +8907,10 @@
         <v>15</v>
       </c>
       <c r="H63" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I63" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J63" t="n">
         <v>15</v>
@@ -7621,7 +8937,7 @@
         <v>2</v>
       </c>
       <c r="R63" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="S63" t="n">
         <v>36</v>
@@ -7675,6 +8991,27 @@
         <v>1</v>
       </c>
       <c r="AJ63" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK63" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL63" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM63" t="n">
+        <v>3770</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>19.76127320954907</v>
+      </c>
+      <c r="AO63" t="n">
+        <v>15</v>
+      </c>
+      <c r="AP63" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ63" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7702,13 +9039,13 @@
         <v>24.72113355441664</v>
       </c>
       <c r="G64" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H64" t="n">
         <v>70</v>
       </c>
       <c r="I64" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J64" t="n">
         <v>6</v>
@@ -7789,6 +9126,27 @@
         <v>0</v>
       </c>
       <c r="AJ64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM64" t="n">
+        <v>3317</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>24.72113355441664</v>
+      </c>
+      <c r="AO64" t="n">
+        <v>14</v>
+      </c>
+      <c r="AP64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ64" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7819,7 +9177,7 @@
         <v>10</v>
       </c>
       <c r="H65" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I65" t="n">
         <v>51</v>
@@ -7834,7 +9192,7 @@
         <v>11</v>
       </c>
       <c r="M65" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N65" t="n">
         <v>2</v>
@@ -7903,6 +9261,27 @@
         <v>0</v>
       </c>
       <c r="AJ65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM65" t="n">
+        <v>3331</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>0.6904833383368358</v>
+      </c>
+      <c r="AO65" t="n">
+        <v>28</v>
+      </c>
+      <c r="AP65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ65" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7933,7 +9312,7 @@
         <v>13</v>
       </c>
       <c r="H66" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I66" t="n">
         <v>34</v>
@@ -8018,6 +9397,27 @@
       </c>
       <c r="AJ66" t="n">
         <v>2</v>
+      </c>
+      <c r="AK66" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL66" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM66" t="n">
+        <v>3265</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>26.4624808575804</v>
+      </c>
+      <c r="AO66" t="n">
+        <v>9</v>
+      </c>
+      <c r="AP66" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -8133,6 +9533,27 @@
       <c r="AJ67" t="n">
         <v>0</v>
       </c>
+      <c r="AK67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ67" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -8247,6 +9668,27 @@
       <c r="AJ68" t="n">
         <v>0</v>
       </c>
+      <c r="AK68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM68" t="n">
+        <v>2964</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>35.1889338731444</v>
+      </c>
+      <c r="AO68" t="n">
+        <v>16</v>
+      </c>
+      <c r="AP68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ68" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -8260,7 +9702,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D69" t="n">
         <v>2108</v>
@@ -8278,7 +9720,7 @@
         <v>30</v>
       </c>
       <c r="I69" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J69" t="n">
         <v>3</v>
@@ -8359,6 +9801,27 @@
         <v>1</v>
       </c>
       <c r="AJ69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK69" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM69" t="n">
+        <v>2108</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>45.63567362428842</v>
+      </c>
+      <c r="AO69" t="n">
+        <v>11</v>
+      </c>
+      <c r="AP69" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ69" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8389,13 +9852,13 @@
         <v>15</v>
       </c>
       <c r="H70" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I70" t="n">
         <v>26</v>
       </c>
       <c r="J70" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K70" t="n">
         <v>16</v>
@@ -8473,6 +9936,27 @@
         <v>0</v>
       </c>
       <c r="AJ70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM70" t="n">
+        <v>2945</v>
+      </c>
+      <c r="AN70" t="n">
+        <v>5.093378607809847</v>
+      </c>
+      <c r="AO70" t="n">
+        <v>9</v>
+      </c>
+      <c r="AP70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ70" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8488,7 +9972,7 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D71" t="n">
         <v>3279</v>
@@ -8557,7 +10041,7 @@
         <v>6</v>
       </c>
       <c r="Z71" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA71" t="n">
         <v>5</v>
@@ -8587,6 +10071,27 @@
         <v>0</v>
       </c>
       <c r="AJ71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM71" t="n">
+        <v>3279</v>
+      </c>
+      <c r="AN71" t="n">
+        <v>52.02805733455321</v>
+      </c>
+      <c r="AO71" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ71" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8703,6 +10208,27 @@
       <c r="AJ72" t="n">
         <v>1</v>
       </c>
+      <c r="AK72" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM72" t="n">
+        <v>4384</v>
+      </c>
+      <c r="AN72" t="n">
+        <v>43.75</v>
+      </c>
+      <c r="AO72" t="n">
+        <v>20</v>
+      </c>
+      <c r="AP72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ72" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -8716,7 +10242,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D73" t="n">
         <v>2434</v>
@@ -8815,6 +10341,27 @@
         <v>1</v>
       </c>
       <c r="AJ73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM73" t="n">
+        <v>2434</v>
+      </c>
+      <c r="AN73" t="n">
+        <v>2.29252259654889</v>
+      </c>
+      <c r="AO73" t="n">
+        <v>11</v>
+      </c>
+      <c r="AP73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ73" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8848,7 +10395,7 @@
         <v>86</v>
       </c>
       <c r="I74" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="J74" t="n">
         <v>22</v>
@@ -8930,6 +10477,27 @@
       </c>
       <c r="AJ74" t="n">
         <v>2</v>
+      </c>
+      <c r="AK74" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL74" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM74" t="n">
+        <v>5112</v>
+      </c>
+      <c r="AN74" t="n">
+        <v>31.8075117370892</v>
+      </c>
+      <c r="AO74" t="n">
+        <v>24</v>
+      </c>
+      <c r="AP74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ74" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -8944,7 +10512,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D75" t="n">
         <v>3249</v>
@@ -8962,13 +10530,13 @@
         <v>38</v>
       </c>
       <c r="I75" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J75" t="n">
         <v>14</v>
       </c>
       <c r="K75" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L75" t="n">
         <v>16</v>
@@ -8989,7 +10557,7 @@
         <v>4</v>
       </c>
       <c r="R75" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="S75" t="n">
         <v>31</v>
@@ -9004,19 +10572,19 @@
         <v>0</v>
       </c>
       <c r="W75" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="X75" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y75" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z75" t="n">
         <v>1</v>
       </c>
       <c r="AA75" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB75" t="n">
         <v>2</v>
@@ -9043,6 +10611,27 @@
         <v>1</v>
       </c>
       <c r="AJ75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>3249</v>
+      </c>
+      <c r="AN75" t="n">
+        <v>11.14188981224992</v>
+      </c>
+      <c r="AO75" t="n">
+        <v>11</v>
+      </c>
+      <c r="AP75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ75" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9076,7 +10665,7 @@
         <v>38</v>
       </c>
       <c r="I76" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J76" t="n">
         <v>11</v>
@@ -9157,6 +10746,27 @@
         <v>1</v>
       </c>
       <c r="AJ76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK76" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM76" t="n">
+        <v>2752</v>
+      </c>
+      <c r="AN76" t="n">
+        <v>16.96947674418605</v>
+      </c>
+      <c r="AO76" t="n">
+        <v>12</v>
+      </c>
+      <c r="AP76" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ76" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9196,10 +10806,10 @@
         <v>14</v>
       </c>
       <c r="K77" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L77" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M77" t="n">
         <v>29</v>
@@ -9235,7 +10845,7 @@
         <v>8</v>
       </c>
       <c r="X77" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y77" t="n">
         <v>7</v>
@@ -9271,6 +10881,27 @@
         <v>2</v>
       </c>
       <c r="AJ77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK77" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM77" t="n">
+        <v>3280</v>
+      </c>
+      <c r="AN77" t="n">
+        <v>21.12804878048781</v>
+      </c>
+      <c r="AO77" t="n">
+        <v>11</v>
+      </c>
+      <c r="AP77" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ77" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9334,7 +10965,7 @@
         <v>16</v>
       </c>
       <c r="S78" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="T78" t="n">
         <v>2</v>
@@ -9385,6 +11016,27 @@
         <v>1</v>
       </c>
       <c r="AJ78" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK78" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL78" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM78" t="n">
+        <v>3339</v>
+      </c>
+      <c r="AN78" t="n">
+        <v>13.50703803533992</v>
+      </c>
+      <c r="AO78" t="n">
+        <v>13</v>
+      </c>
+      <c r="AP78" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ78" t="n">
         <v>1</v>
       </c>
     </row>
@@ -9501,6 +11153,27 @@
       <c r="AJ79" t="n">
         <v>0</v>
       </c>
+      <c r="AK79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM79" t="n">
+        <v>337</v>
+      </c>
+      <c r="AN79" t="n">
+        <v>100</v>
+      </c>
+      <c r="AO79" t="n">
+        <v>7</v>
+      </c>
+      <c r="AP79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ79" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -9514,7 +11187,7 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D80" t="n">
         <v>7541</v>
@@ -9529,7 +11202,7 @@
         <v>22</v>
       </c>
       <c r="H80" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I80" t="n">
         <v>71</v>
@@ -9550,7 +11223,7 @@
         <v>6</v>
       </c>
       <c r="O80" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P80" t="n">
         <v>4</v>
@@ -9614,6 +11287,27 @@
       </c>
       <c r="AJ80" t="n">
         <v>5</v>
+      </c>
+      <c r="AK80" t="n">
+        <v>8</v>
+      </c>
+      <c r="AL80" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM80" t="n">
+        <v>7541</v>
+      </c>
+      <c r="AN80" t="n">
+        <v>7.837156875745922</v>
+      </c>
+      <c r="AO80" t="n">
+        <v>26</v>
+      </c>
+      <c r="AP80" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ80" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="81">
@@ -9643,7 +11337,7 @@
         <v>20</v>
       </c>
       <c r="H81" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I81" t="n">
         <v>39</v>
@@ -9676,7 +11370,7 @@
         <v>19</v>
       </c>
       <c r="S81" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="T81" t="n">
         <v>2</v>
@@ -9712,7 +11406,7 @@
         <v>6</v>
       </c>
       <c r="AE81" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF81" t="n">
         <v>1</v>
@@ -9727,6 +11421,27 @@
         <v>3</v>
       </c>
       <c r="AJ81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK81" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM81" t="n">
+        <v>3618</v>
+      </c>
+      <c r="AN81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO81" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ81" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9754,7 +11469,7 @@
         <v>9.207525655644242</v>
       </c>
       <c r="G82" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H82" t="n">
         <v>78</v>
@@ -9841,6 +11556,27 @@
         <v>1</v>
       </c>
       <c r="AJ82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK82" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM82" t="n">
+        <v>3508</v>
+      </c>
+      <c r="AN82" t="n">
+        <v>9.207525655644242</v>
+      </c>
+      <c r="AO82" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP82" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ82" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9856,7 +11592,7 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D83" t="n">
         <v>3753</v>
@@ -9874,7 +11610,7 @@
         <v>59</v>
       </c>
       <c r="I83" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J83" t="n">
         <v>12</v>
@@ -9901,10 +11637,10 @@
         <v>7</v>
       </c>
       <c r="R83" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S83" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="T83" t="n">
         <v>3</v>
@@ -9955,6 +11691,27 @@
         <v>0</v>
       </c>
       <c r="AJ83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM83" t="n">
+        <v>3753</v>
+      </c>
+      <c r="AN83" t="n">
+        <v>2.504662936317612</v>
+      </c>
+      <c r="AO83" t="n">
+        <v>11</v>
+      </c>
+      <c r="AP83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ83" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10071,6 +11828,27 @@
       <c r="AJ84" t="n">
         <v>1</v>
       </c>
+      <c r="AK84" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL84" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM84" t="n">
+        <v>3270</v>
+      </c>
+      <c r="AN84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO84" t="n">
+        <v>12</v>
+      </c>
+      <c r="AP84" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ84" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -10099,10 +11877,10 @@
         <v>6</v>
       </c>
       <c r="H85" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I85" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J85" t="n">
         <v>17</v>
@@ -10114,13 +11892,13 @@
         <v>19</v>
       </c>
       <c r="M85" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N85" t="n">
         <v>4</v>
       </c>
       <c r="O85" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P85" t="n">
         <v>4</v>
@@ -10183,6 +11961,27 @@
         <v>2</v>
       </c>
       <c r="AJ85" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK85" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL85" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM85" t="n">
+        <v>3281</v>
+      </c>
+      <c r="AN85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO85" t="n">
+        <v>12</v>
+      </c>
+      <c r="AP85" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ85" t="n">
         <v>1</v>
       </c>
     </row>
@@ -10213,7 +12012,7 @@
         <v>14</v>
       </c>
       <c r="H86" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I86" t="n">
         <v>34</v>
@@ -10246,7 +12045,7 @@
         <v>26</v>
       </c>
       <c r="S86" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="T86" t="n">
         <v>4</v>
@@ -10297,6 +12096,27 @@
         <v>1</v>
       </c>
       <c r="AJ86" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK86" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL86" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM86" t="n">
+        <v>3916</v>
+      </c>
+      <c r="AN86" t="n">
+        <v>0.4596527068437181</v>
+      </c>
+      <c r="AO86" t="n">
+        <v>11</v>
+      </c>
+      <c r="AP86" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ86" t="n">
         <v>1</v>
       </c>
     </row>
@@ -10327,10 +12147,10 @@
         <v>12</v>
       </c>
       <c r="H87" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I87" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J87" t="n">
         <v>12</v>
@@ -10411,6 +12231,27 @@
         <v>2</v>
       </c>
       <c r="AJ87" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK87" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL87" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM87" t="n">
+        <v>3951</v>
+      </c>
+      <c r="AN87" t="n">
+        <v>0.9111617312072893</v>
+      </c>
+      <c r="AO87" t="n">
+        <v>11</v>
+      </c>
+      <c r="AP87" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ87" t="n">
         <v>1</v>
       </c>
     </row>
@@ -10441,10 +12282,10 @@
         <v>10</v>
       </c>
       <c r="H88" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I88" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="J88" t="n">
         <v>13</v>
@@ -10456,7 +12297,7 @@
         <v>28</v>
       </c>
       <c r="M88" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N88" t="n">
         <v>6</v>
@@ -10525,6 +12366,27 @@
         <v>3</v>
       </c>
       <c r="AJ88" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK88" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL88" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM88" t="n">
+        <v>3895</v>
+      </c>
+      <c r="AN88" t="n">
+        <v>3.902439024390244</v>
+      </c>
+      <c r="AO88" t="n">
+        <v>15</v>
+      </c>
+      <c r="AP88" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ88" t="n">
         <v>1</v>
       </c>
     </row>
@@ -10558,7 +12420,7 @@
         <v>76</v>
       </c>
       <c r="I89" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J89" t="n">
         <v>7</v>
@@ -10639,6 +12501,27 @@
         <v>1</v>
       </c>
       <c r="AJ89" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK89" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL89" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM89" t="n">
+        <v>3476</v>
+      </c>
+      <c r="AN89" t="n">
+        <v>23.67663981588032</v>
+      </c>
+      <c r="AO89" t="n">
+        <v>13</v>
+      </c>
+      <c r="AP89" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ89" t="n">
         <v>1</v>
       </c>
     </row>
@@ -10693,7 +12576,7 @@
         <v>7</v>
       </c>
       <c r="P90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q90" t="n">
         <v>12</v>
@@ -10729,7 +12612,7 @@
         <v>5</v>
       </c>
       <c r="AB90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC90" t="n">
         <v>6</v>
@@ -10753,6 +12636,27 @@
         <v>0</v>
       </c>
       <c r="AJ90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM90" t="n">
+        <v>3508</v>
+      </c>
+      <c r="AN90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO90" t="n">
+        <v>14</v>
+      </c>
+      <c r="AP90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ90" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10869,6 +12773,27 @@
       <c r="AJ91" t="n">
         <v>0</v>
       </c>
+      <c r="AK91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM91" t="n">
+        <v>3531</v>
+      </c>
+      <c r="AN91" t="n">
+        <v>8.496176720475786</v>
+      </c>
+      <c r="AO91" t="n">
+        <v>13</v>
+      </c>
+      <c r="AP91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ91" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -10897,13 +12822,13 @@
         <v>10</v>
       </c>
       <c r="H92" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I92" t="n">
         <v>34</v>
       </c>
       <c r="J92" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K92" t="n">
         <v>5</v>
@@ -10927,10 +12852,10 @@
         <v>7</v>
       </c>
       <c r="R92" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S92" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="T92" t="n">
         <v>0</v>
@@ -10981,6 +12906,27 @@
         <v>1</v>
       </c>
       <c r="AJ92" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK92" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL92" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM92" t="n">
+        <v>3702</v>
+      </c>
+      <c r="AN92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO92" t="n">
+        <v>11</v>
+      </c>
+      <c r="AP92" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ92" t="n">
         <v>1</v>
       </c>
     </row>
@@ -11011,7 +12957,7 @@
         <v>21</v>
       </c>
       <c r="H93" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I93" t="n">
         <v>44</v>
@@ -11020,7 +12966,7 @@
         <v>15</v>
       </c>
       <c r="K93" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L93" t="n">
         <v>15</v>
@@ -11059,7 +13005,7 @@
         <v>10</v>
       </c>
       <c r="X93" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y93" t="n">
         <v>8</v>
@@ -11095,6 +13041,27 @@
         <v>2</v>
       </c>
       <c r="AJ93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK93" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM93" t="n">
+        <v>3772</v>
+      </c>
+      <c r="AN93" t="n">
+        <v>25.02651113467656</v>
+      </c>
+      <c r="AO93" t="n">
+        <v>13</v>
+      </c>
+      <c r="AP93" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ93" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11125,13 +13092,13 @@
         <v>16</v>
       </c>
       <c r="H94" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I94" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J94" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K94" t="n">
         <v>14</v>
@@ -11209,6 +13176,27 @@
         <v>1</v>
       </c>
       <c r="AJ94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK94" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM94" t="n">
+        <v>3624</v>
+      </c>
+      <c r="AN94" t="n">
+        <v>41.30794701986755</v>
+      </c>
+      <c r="AO94" t="n">
+        <v>9</v>
+      </c>
+      <c r="AP94" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ94" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11254,7 +13242,7 @@
         <v>14</v>
       </c>
       <c r="M95" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N95" t="n">
         <v>6</v>
@@ -11272,7 +13260,7 @@
         <v>29</v>
       </c>
       <c r="S95" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="T95" t="n">
         <v>3</v>
@@ -11323,6 +13311,27 @@
         <v>2</v>
       </c>
       <c r="AJ95" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK95" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL95" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM95" t="n">
+        <v>3536</v>
+      </c>
+      <c r="AN95" t="n">
+        <v>9.219457013574662</v>
+      </c>
+      <c r="AO95" t="n">
+        <v>11</v>
+      </c>
+      <c r="AP95" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ95" t="n">
         <v>1</v>
       </c>
     </row>
@@ -11353,10 +13362,10 @@
         <v>16</v>
       </c>
       <c r="H96" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I96" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J96" t="n">
         <v>17</v>
@@ -11374,7 +13383,7 @@
         <v>5</v>
       </c>
       <c r="O96" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P96" t="n">
         <v>2</v>
@@ -11438,6 +13447,27 @@
       </c>
       <c r="AJ96" t="n">
         <v>2</v>
+      </c>
+      <c r="AK96" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL96" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM96" t="n">
+        <v>3629</v>
+      </c>
+      <c r="AN96" t="n">
+        <v>5.12537889225682</v>
+      </c>
+      <c r="AO96" t="n">
+        <v>11</v>
+      </c>
+      <c r="AP96" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ96" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="97">
@@ -11553,6 +13583,27 @@
       <c r="AJ97" t="n">
         <v>1</v>
       </c>
+      <c r="AK97" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL97" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM97" t="n">
+        <v>3728</v>
+      </c>
+      <c r="AN97" t="n">
+        <v>14.64592274678111</v>
+      </c>
+      <c r="AO97" t="n">
+        <v>19</v>
+      </c>
+      <c r="AP97" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ97" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -11584,13 +13635,13 @@
         <v>60</v>
       </c>
       <c r="I98" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J98" t="n">
         <v>18</v>
       </c>
       <c r="K98" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L98" t="n">
         <v>15</v>
@@ -11665,6 +13716,27 @@
         <v>1</v>
       </c>
       <c r="AJ98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK98" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM98" t="n">
+        <v>3608</v>
+      </c>
+      <c r="AN98" t="n">
+        <v>24.27937915742794</v>
+      </c>
+      <c r="AO98" t="n">
+        <v>9</v>
+      </c>
+      <c r="AP98" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ98" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11781,6 +13853,27 @@
       <c r="AJ99" t="n">
         <v>0</v>
       </c>
+      <c r="AK99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM99" t="n">
+        <v>3396</v>
+      </c>
+      <c r="AN99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO99" t="n">
+        <v>14</v>
+      </c>
+      <c r="AP99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ99" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -11809,10 +13902,10 @@
         <v>9</v>
       </c>
       <c r="H100" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I100" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J100" t="n">
         <v>16</v>
@@ -11833,7 +13926,7 @@
         <v>3</v>
       </c>
       <c r="P100" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q100" t="n">
         <v>13</v>
@@ -11893,6 +13986,27 @@
         <v>2</v>
       </c>
       <c r="AJ100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK100" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM100" t="n">
+        <v>3379</v>
+      </c>
+      <c r="AN100" t="n">
+        <v>4.350399526487126</v>
+      </c>
+      <c r="AO100" t="n">
+        <v>11</v>
+      </c>
+      <c r="AP100" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ100" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12009,6 +14123,27 @@
       <c r="AJ101" t="n">
         <v>1</v>
       </c>
+      <c r="AK101" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL101" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM101" t="n">
+        <v>3879</v>
+      </c>
+      <c r="AN101" t="n">
+        <v>7.759731889662285</v>
+      </c>
+      <c r="AO101" t="n">
+        <v>13</v>
+      </c>
+      <c r="AP101" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ101" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -12037,7 +14172,7 @@
         <v>7</v>
       </c>
       <c r="H102" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I102" t="n">
         <v>49</v>
@@ -12067,7 +14202,7 @@
         <v>1</v>
       </c>
       <c r="R102" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="S102" t="n">
         <v>25</v>
@@ -12121,6 +14256,27 @@
         <v>1</v>
       </c>
       <c r="AJ102" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK102" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL102" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM102" t="n">
+        <v>3482</v>
+      </c>
+      <c r="AN102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO102" t="n">
+        <v>11</v>
+      </c>
+      <c r="AP102" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ102" t="n">
         <v>1</v>
       </c>
     </row>
@@ -12136,7 +14292,7 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D103" t="n">
         <v>3495</v>
@@ -12163,7 +14319,7 @@
         <v>25</v>
       </c>
       <c r="L103" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M103" t="n">
         <v>21</v>
@@ -12235,6 +14391,27 @@
         <v>1</v>
       </c>
       <c r="AJ103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK103" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM103" t="n">
+        <v>3495</v>
+      </c>
+      <c r="AN103" t="n">
+        <v>4.062947067238913</v>
+      </c>
+      <c r="AO103" t="n">
+        <v>12</v>
+      </c>
+      <c r="AP103" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ103" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12351,6 +14528,27 @@
       <c r="AJ104" t="n">
         <v>0</v>
       </c>
+      <c r="AK104" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM104" t="n">
+        <v>2605</v>
+      </c>
+      <c r="AN104" t="n">
+        <v>6.602687140115163</v>
+      </c>
+      <c r="AO104" t="n">
+        <v>11</v>
+      </c>
+      <c r="AP104" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ104" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -12412,7 +14610,7 @@
         <v>23</v>
       </c>
       <c r="S105" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T105" t="n">
         <v>7</v>
@@ -12448,7 +14646,7 @@
         <v>3</v>
       </c>
       <c r="AE105" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF105" t="n">
         <v>4</v>
@@ -12464,6 +14662,27 @@
       </c>
       <c r="AJ105" t="n">
         <v>2</v>
+      </c>
+      <c r="AK105" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL105" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM105" t="n">
+        <v>3619</v>
+      </c>
+      <c r="AN105" t="n">
+        <v>7.598784194528875</v>
+      </c>
+      <c r="AO105" t="n">
+        <v>15</v>
+      </c>
+      <c r="AP105" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ105" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="106">
@@ -12508,7 +14727,7 @@
         <v>15</v>
       </c>
       <c r="M106" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N106" t="n">
         <v>2</v>
@@ -12523,7 +14742,7 @@
         <v>10</v>
       </c>
       <c r="R106" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="S106" t="n">
         <v>19</v>
@@ -12578,6 +14797,27 @@
       </c>
       <c r="AJ106" t="n">
         <v>2</v>
+      </c>
+      <c r="AK106" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL106" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM106" t="n">
+        <v>3039</v>
+      </c>
+      <c r="AN106" t="n">
+        <v>10.82592958209938</v>
+      </c>
+      <c r="AO106" t="n">
+        <v>15</v>
+      </c>
+      <c r="AP106" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ106" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="107">
@@ -12610,7 +14850,7 @@
         <v>38</v>
       </c>
       <c r="I107" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J107" t="n">
         <v>6</v>
@@ -12628,10 +14868,10 @@
         <v>4</v>
       </c>
       <c r="O107" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P107" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q107" t="n">
         <v>7</v>
@@ -12652,7 +14892,7 @@
         <v>0</v>
       </c>
       <c r="W107" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X107" t="n">
         <v>7</v>
@@ -12667,7 +14907,7 @@
         <v>4</v>
       </c>
       <c r="AB107" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC107" t="n">
         <v>5</v>
@@ -12691,6 +14931,27 @@
         <v>1</v>
       </c>
       <c r="AJ107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK107" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM107" t="n">
+        <v>4124</v>
+      </c>
+      <c r="AN107" t="n">
+        <v>1.115421920465567</v>
+      </c>
+      <c r="AO107" t="n">
+        <v>13</v>
+      </c>
+      <c r="AP107" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ107" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12807,6 +15068,27 @@
       <c r="AJ108" t="n">
         <v>1</v>
       </c>
+      <c r="AK108" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL108" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM108" t="n">
+        <v>3338</v>
+      </c>
+      <c r="AN108" t="n">
+        <v>24.80527261833433</v>
+      </c>
+      <c r="AO108" t="n">
+        <v>11</v>
+      </c>
+      <c r="AP108" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ108" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -12835,10 +15117,10 @@
         <v>11</v>
       </c>
       <c r="H109" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I109" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J109" t="n">
         <v>12</v>
@@ -12919,6 +15201,27 @@
         <v>1</v>
       </c>
       <c r="AJ109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK109" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM109" t="n">
+        <v>3141</v>
+      </c>
+      <c r="AN109" t="n">
+        <v>21.13976440624005</v>
+      </c>
+      <c r="AO109" t="n">
+        <v>12</v>
+      </c>
+      <c r="AP109" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ109" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12934,7 +15237,7 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D110" t="n">
         <v>2693</v>
@@ -12952,7 +15255,7 @@
         <v>41</v>
       </c>
       <c r="I110" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J110" t="n">
         <v>22</v>
@@ -13033,6 +15336,27 @@
         <v>1</v>
       </c>
       <c r="AJ110" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK110" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL110" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM110" t="n">
+        <v>2693</v>
+      </c>
+      <c r="AN110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO110" t="n">
+        <v>15</v>
+      </c>
+      <c r="AP110" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ110" t="n">
         <v>1</v>
       </c>
     </row>
@@ -13149,6 +15473,27 @@
       <c r="AJ111" t="n">
         <v>0</v>
       </c>
+      <c r="AK111" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM111" t="n">
+        <v>3024</v>
+      </c>
+      <c r="AN111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO111" t="n">
+        <v>15</v>
+      </c>
+      <c r="AP111" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ111" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -13162,7 +15507,7 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D112" t="n">
         <v>3704</v>
@@ -13177,7 +15522,7 @@
         <v>17</v>
       </c>
       <c r="H112" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="I112" t="n">
         <v>24</v>
@@ -13207,7 +15552,7 @@
         <v>2</v>
       </c>
       <c r="R112" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S112" t="n">
         <v>19</v>
@@ -13243,7 +15588,7 @@
         <v>2</v>
       </c>
       <c r="AD112" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE112" t="n">
         <v>4</v>
@@ -13261,6 +15606,27 @@
         <v>0</v>
       </c>
       <c r="AJ112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM112" t="n">
+        <v>3704</v>
+      </c>
+      <c r="AN112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO112" t="n">
+        <v>16</v>
+      </c>
+      <c r="AP112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ112" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13294,7 +15660,7 @@
         <v>40</v>
       </c>
       <c r="I113" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J113" t="n">
         <v>14</v>
@@ -13375,6 +15741,27 @@
         <v>0</v>
       </c>
       <c r="AJ113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM113" t="n">
+        <v>3697</v>
+      </c>
+      <c r="AN113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO113" t="n">
+        <v>12</v>
+      </c>
+      <c r="AP113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ113" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13390,7 +15777,7 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D114" t="n">
         <v>3611</v>
@@ -13405,7 +15792,7 @@
         <v>8</v>
       </c>
       <c r="H114" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I114" t="n">
         <v>35</v>
@@ -13417,7 +15804,7 @@
         <v>28</v>
       </c>
       <c r="L114" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M114" t="n">
         <v>29</v>
@@ -13489,6 +15876,27 @@
         <v>3</v>
       </c>
       <c r="AJ114" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK114" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL114" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM114" t="n">
+        <v>3611</v>
+      </c>
+      <c r="AN114" t="n">
+        <v>9.858764885073388</v>
+      </c>
+      <c r="AO114" t="n">
+        <v>14</v>
+      </c>
+      <c r="AP114" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ114" t="n">
         <v>1</v>
       </c>
     </row>
@@ -13504,7 +15912,7 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D115" t="n">
         <v>3016</v>
@@ -13519,7 +15927,7 @@
         <v>15</v>
       </c>
       <c r="H115" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I115" t="n">
         <v>24</v>
@@ -13603,6 +16011,27 @@
         <v>1</v>
       </c>
       <c r="AJ115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK115" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM115" t="n">
+        <v>3016</v>
+      </c>
+      <c r="AN115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO115" t="n">
+        <v>9</v>
+      </c>
+      <c r="AP115" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ115" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13633,7 +16062,7 @@
         <v>13</v>
       </c>
       <c r="H116" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I116" t="n">
         <v>21</v>
@@ -13717,6 +16146,27 @@
         <v>0</v>
       </c>
       <c r="AJ116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM116" t="n">
+        <v>3251</v>
+      </c>
+      <c r="AN116" t="n">
+        <v>0.3383574284835435</v>
+      </c>
+      <c r="AO116" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ116" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13833,6 +16283,27 @@
       <c r="AJ117" t="n">
         <v>2</v>
       </c>
+      <c r="AK117" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>3685</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>32.64586160108548</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>19</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -13846,7 +16317,7 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D118" t="n">
         <v>3120</v>
@@ -13945,6 +16416,27 @@
         <v>2</v>
       </c>
       <c r="AJ118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>3120</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>14</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ118" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13975,7 +16467,7 @@
         <v>13</v>
       </c>
       <c r="H119" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I119" t="n">
         <v>39</v>
@@ -13993,10 +16485,10 @@
         <v>44</v>
       </c>
       <c r="N119" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O119" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P119" t="n">
         <v>8</v>
@@ -14008,7 +16500,7 @@
         <v>24</v>
       </c>
       <c r="S119" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T119" t="n">
         <v>6</v>
@@ -14059,6 +16551,27 @@
         <v>2</v>
       </c>
       <c r="AJ119" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>4203</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>20.19985724482513</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>11</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ119" t="n">
         <v>1</v>
       </c>
     </row>
@@ -14074,7 +16587,7 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D120" t="n">
         <v>4005</v>
@@ -14092,7 +16605,7 @@
         <v>39</v>
       </c>
       <c r="I120" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="J120" t="n">
         <v>21</v>
@@ -14122,7 +16635,7 @@
         <v>23</v>
       </c>
       <c r="S120" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="T120" t="n">
         <v>8</v>
@@ -14173,6 +16686,27 @@
         <v>1</v>
       </c>
       <c r="AJ120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>4005</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>1.647940074906367</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>16</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ120" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14188,7 +16722,7 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D121" t="n">
         <v>3411</v>
@@ -14287,6 +16821,27 @@
         <v>2</v>
       </c>
       <c r="AJ121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>3411</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>4.690706537672237</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>12</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ121" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14317,7 +16872,7 @@
         <v>16</v>
       </c>
       <c r="H122" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I122" t="n">
         <v>40</v>
@@ -14329,7 +16884,7 @@
         <v>12</v>
       </c>
       <c r="L122" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M122" t="n">
         <v>18</v>
@@ -14401,6 +16956,27 @@
         <v>2</v>
       </c>
       <c r="AJ122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>2415</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>16.77018633540373</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>12</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ122" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14431,7 +17007,7 @@
         <v>24</v>
       </c>
       <c r="H123" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I123" t="n">
         <v>56</v>
@@ -14515,6 +17091,27 @@
         <v>1</v>
       </c>
       <c r="AJ123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>3256</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>12.19287469287469</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>17</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ123" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14545,19 +17142,19 @@
         <v>19</v>
       </c>
       <c r="H124" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="I124" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="J124" t="n">
         <v>26</v>
       </c>
       <c r="K124" t="n">
+        <v>17</v>
+      </c>
+      <c r="L124" t="n">
         <v>16</v>
-      </c>
-      <c r="L124" t="n">
-        <v>15</v>
       </c>
       <c r="M124" t="n">
         <v>37</v>
@@ -14566,7 +17163,7 @@
         <v>4</v>
       </c>
       <c r="O124" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P124" t="n">
         <v>9</v>
@@ -14578,7 +17175,7 @@
         <v>29</v>
       </c>
       <c r="S124" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="T124" t="n">
         <v>6</v>
@@ -14629,6 +17226,27 @@
         <v>3</v>
       </c>
       <c r="AJ124" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>5667</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>36.2802188106582</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>25</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ124" t="n">
         <v>1</v>
       </c>
     </row>
@@ -14745,6 +17363,27 @@
       <c r="AJ125" t="n">
         <v>1</v>
       </c>
+      <c r="AK125" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>4147</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>11.55051844707017</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>20</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -14776,13 +17415,13 @@
         <v>73</v>
       </c>
       <c r="I126" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="J126" t="n">
         <v>18</v>
       </c>
       <c r="K126" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L126" t="n">
         <v>10</v>
@@ -14818,7 +17457,7 @@
         <v>0</v>
       </c>
       <c r="W126" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="X126" t="n">
         <v>14</v>
@@ -14857,6 +17496,27 @@
         <v>3</v>
       </c>
       <c r="AJ126" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>5371</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>89.81567678272202</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>24</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ126" t="n">
         <v>1</v>
       </c>
     </row>
@@ -14890,7 +17550,7 @@
         <v>36</v>
       </c>
       <c r="I127" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J127" t="n">
         <v>14</v>
@@ -14971,6 +17631,27 @@
         <v>1</v>
       </c>
       <c r="AJ127" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>3810</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>28.24146981627297</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ127" t="n">
         <v>1</v>
       </c>
     </row>
@@ -15016,7 +17697,7 @@
         <v>18</v>
       </c>
       <c r="M128" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N128" t="n">
         <v>8</v>
@@ -15085,6 +17766,27 @@
         <v>0</v>
       </c>
       <c r="AJ128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>3450</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>12</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ128" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15201,6 +17903,27 @@
       <c r="AJ129" t="n">
         <v>1</v>
       </c>
+      <c r="AK129" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>3877</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>5.08124838792881</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>14</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -15259,7 +17982,7 @@
         <v>5</v>
       </c>
       <c r="R130" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S130" t="n">
         <v>35</v>
@@ -15313,6 +18036,27 @@
         <v>1</v>
       </c>
       <c r="AJ130" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>3835</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>13.16818774445893</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>12</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ130" t="n">
         <v>1</v>
       </c>
     </row>
@@ -15346,7 +18090,7 @@
         <v>62</v>
       </c>
       <c r="I131" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J131" t="n">
         <v>17</v>
@@ -15427,6 +18171,27 @@
         <v>4</v>
       </c>
       <c r="AJ131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>5822</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>48.8663689453796</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>25</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ131" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15457,7 +18222,7 @@
         <v>27</v>
       </c>
       <c r="H132" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I132" t="n">
         <v>5</v>
@@ -15541,6 +18306,27 @@
         <v>1</v>
       </c>
       <c r="AJ132" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>3196</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>19.36795994993742</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>17</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ132" t="n">
         <v>1</v>
       </c>
     </row>
@@ -15574,7 +18360,7 @@
         <v>55</v>
       </c>
       <c r="I133" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J133" t="n">
         <v>19</v>
@@ -15655,6 +18441,27 @@
         <v>0</v>
       </c>
       <c r="AJ133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>3437</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>8.61216176898458</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>16</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ133" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15688,7 +18495,7 @@
         <v>39</v>
       </c>
       <c r="I134" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J134" t="n">
         <v>13</v>
@@ -15700,7 +18507,7 @@
         <v>13</v>
       </c>
       <c r="M134" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N134" t="n">
         <v>4</v>
@@ -15769,6 +18576,27 @@
         <v>1</v>
       </c>
       <c r="AJ134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>3993</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>14.9511645379414</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>13</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ134" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15799,7 +18627,7 @@
         <v>15</v>
       </c>
       <c r="H135" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I135" t="n">
         <v>48</v>
@@ -15823,13 +18651,13 @@
         <v>7</v>
       </c>
       <c r="P135" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q135" t="n">
         <v>7</v>
       </c>
       <c r="R135" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="S135" t="n">
         <v>28</v>
@@ -15883,6 +18711,27 @@
         <v>1</v>
       </c>
       <c r="AJ135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>3654</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>16.83087027914614</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>11</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ135" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15913,7 +18762,7 @@
         <v>16</v>
       </c>
       <c r="H136" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I136" t="n">
         <v>34</v>
@@ -15928,7 +18777,7 @@
         <v>12</v>
       </c>
       <c r="M136" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="N136" t="n">
         <v>1</v>
@@ -15946,7 +18795,7 @@
         <v>28</v>
       </c>
       <c r="S136" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="T136" t="n">
         <v>2</v>
@@ -15982,7 +18831,7 @@
         <v>9</v>
       </c>
       <c r="AE136" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AF136" t="n">
         <v>2</v>
@@ -15998,6 +18847,27 @@
       </c>
       <c r="AJ136" t="n">
         <v>2</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>5378</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>38.91781331349944</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>27</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="137">
@@ -16036,7 +18906,7 @@
         <v>22</v>
       </c>
       <c r="K137" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L137" t="n">
         <v>20</v>
@@ -16111,6 +18981,27 @@
         <v>0</v>
       </c>
       <c r="AJ137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>5670</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>52.01058201058201</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>26</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ137" t="n">
         <v>0</v>
       </c>
     </row>
@@ -16227,6 +19118,27 @@
       <c r="AJ138" t="n">
         <v>0</v>
       </c>
+      <c r="AK138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>3162</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>73.46616065781151</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>14</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -16341,6 +19253,27 @@
       <c r="AJ139" t="n">
         <v>1</v>
       </c>
+      <c r="AK139" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>2496</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>26.04166666666667</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>21</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -16369,7 +19302,7 @@
         <v>11</v>
       </c>
       <c r="H140" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I140" t="n">
         <v>43</v>
@@ -16453,6 +19386,27 @@
         <v>1</v>
       </c>
       <c r="AJ140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>3186</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>11.70747018204645</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ140" t="n">
         <v>0</v>
       </c>
     </row>
@@ -16569,6 +19523,27 @@
       <c r="AJ141" t="n">
         <v>0</v>
       </c>
+      <c r="AK141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>30</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -16600,7 +19575,7 @@
         <v>51</v>
       </c>
       <c r="I142" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J142" t="n">
         <v>23</v>
@@ -16636,7 +19611,7 @@
         <v>0</v>
       </c>
       <c r="U142" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V142" t="n">
         <v>0</v>
@@ -16672,7 +19647,7 @@
         <v>0</v>
       </c>
       <c r="AG142" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH142" t="n">
         <v>0</v>
@@ -16681,6 +19656,27 @@
         <v>2</v>
       </c>
       <c r="AJ142" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>3876</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>12</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ142" t="n">
         <v>1</v>
       </c>
     </row>
@@ -16696,7 +19692,7 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D143" t="n">
         <v>3568</v>
@@ -16795,6 +19791,27 @@
         <v>1</v>
       </c>
       <c r="AJ143" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>3568</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>29.48430493273543</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>11</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ143" t="n">
         <v>1</v>
       </c>
     </row>
@@ -16828,7 +19845,7 @@
         <v>63</v>
       </c>
       <c r="I144" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J144" t="n">
         <v>18</v>
@@ -16864,7 +19881,7 @@
         <v>5</v>
       </c>
       <c r="U144" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="V144" t="n">
         <v>0</v>
@@ -16909,6 +19926,27 @@
         <v>1</v>
       </c>
       <c r="AJ144" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK144" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL144" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM144" t="n">
+        <v>3452</v>
+      </c>
+      <c r="AN144" t="n">
+        <v>4.779837775202781</v>
+      </c>
+      <c r="AO144" t="n">
+        <v>13</v>
+      </c>
+      <c r="AP144" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ144" t="n">
         <v>1</v>
       </c>
     </row>
@@ -17025,6 +20063,27 @@
       <c r="AJ145" t="n">
         <v>0</v>
       </c>
+      <c r="AK145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM145" t="n">
+        <v>48</v>
+      </c>
+      <c r="AN145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO145" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ145" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -17056,7 +20115,7 @@
         <v>75</v>
       </c>
       <c r="I146" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="J146" t="n">
         <v>18</v>
@@ -17068,7 +20127,7 @@
         <v>13</v>
       </c>
       <c r="M146" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N146" t="n">
         <v>7</v>
@@ -17080,7 +20139,7 @@
         <v>8</v>
       </c>
       <c r="Q146" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R146" t="n">
         <v>14</v>
@@ -17116,7 +20175,7 @@
         <v>4</v>
       </c>
       <c r="AC146" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD146" t="n">
         <v>5</v>
@@ -17137,6 +20196,27 @@
         <v>0</v>
       </c>
       <c r="AJ146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM146" t="n">
+        <v>3735</v>
+      </c>
+      <c r="AN146" t="n">
+        <v>31.78045515394913</v>
+      </c>
+      <c r="AO146" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ146" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17200,7 +20280,7 @@
         <v>15</v>
       </c>
       <c r="S147" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T147" t="n">
         <v>0</v>
@@ -17236,7 +20316,7 @@
         <v>5</v>
       </c>
       <c r="AE147" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF147" t="n">
         <v>0</v>
@@ -17251,6 +20331,27 @@
         <v>0</v>
       </c>
       <c r="AJ147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM147" t="n">
+        <v>4118</v>
+      </c>
+      <c r="AN147" t="n">
+        <v>3.011170471102477</v>
+      </c>
+      <c r="AO147" t="n">
+        <v>12</v>
+      </c>
+      <c r="AP147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ147" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17367,6 +20468,27 @@
       <c r="AJ148" t="n">
         <v>1</v>
       </c>
+      <c r="AK148" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL148" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM148" t="n">
+        <v>3771</v>
+      </c>
+      <c r="AN148" t="n">
+        <v>13.97507292495359</v>
+      </c>
+      <c r="AO148" t="n">
+        <v>12</v>
+      </c>
+      <c r="AP148" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ148" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -17380,7 +20502,7 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D149" t="n">
         <v>3933</v>
@@ -17413,7 +20535,7 @@
         <v>32</v>
       </c>
       <c r="N149" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O149" t="n">
         <v>9</v>
@@ -17449,7 +20571,7 @@
         <v>9</v>
       </c>
       <c r="Z149" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA149" t="n">
         <v>4</v>
@@ -17479,6 +20601,27 @@
         <v>1</v>
       </c>
       <c r="AJ149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK149" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM149" t="n">
+        <v>3933</v>
+      </c>
+      <c r="AN149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO149" t="n">
+        <v>13</v>
+      </c>
+      <c r="AP149" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ149" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17494,7 +20637,7 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D150" t="n">
         <v>3770</v>
@@ -17593,6 +20736,27 @@
         <v>2</v>
       </c>
       <c r="AJ150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK150" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM150" t="n">
+        <v>3770</v>
+      </c>
+      <c r="AN150" t="n">
+        <v>67.18832891246684</v>
+      </c>
+      <c r="AO150" t="n">
+        <v>13</v>
+      </c>
+      <c r="AP150" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ150" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17626,7 +20790,7 @@
         <v>57</v>
       </c>
       <c r="I151" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="J151" t="n">
         <v>31</v>
@@ -17638,7 +20802,7 @@
         <v>26</v>
       </c>
       <c r="M151" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="N151" t="n">
         <v>6</v>
@@ -17653,7 +20817,7 @@
         <v>22</v>
       </c>
       <c r="R151" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S151" t="n">
         <v>36</v>
@@ -17707,6 +20871,27 @@
         <v>1</v>
       </c>
       <c r="AJ151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK151" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM151" t="n">
+        <v>3482</v>
+      </c>
+      <c r="AN151" t="n">
+        <v>11.91843767949454</v>
+      </c>
+      <c r="AO151" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP151" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ151" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17749,7 +20934,7 @@
         <v>10</v>
       </c>
       <c r="L152" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M152" t="n">
         <v>23</v>
@@ -17770,7 +20955,7 @@
         <v>25</v>
       </c>
       <c r="S152" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="T152" t="n">
         <v>0</v>
@@ -17821,6 +21006,27 @@
         <v>2</v>
       </c>
       <c r="AJ152" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK152" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL152" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM152" t="n">
+        <v>3288</v>
+      </c>
+      <c r="AN152" t="n">
+        <v>26.36861313868613</v>
+      </c>
+      <c r="AO152" t="n">
+        <v>12</v>
+      </c>
+      <c r="AP152" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ152" t="n">
         <v>1</v>
       </c>
     </row>
@@ -17937,6 +21143,27 @@
       <c r="AJ153" t="n">
         <v>0</v>
       </c>
+      <c r="AK153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM153" t="n">
+        <v>3584</v>
+      </c>
+      <c r="AN153" t="n">
+        <v>32.28236607142857</v>
+      </c>
+      <c r="AO153" t="n">
+        <v>9</v>
+      </c>
+      <c r="AP153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ153" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -17950,7 +21177,7 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D154" t="n">
         <v>3566</v>
@@ -18049,6 +21276,27 @@
         <v>0</v>
       </c>
       <c r="AJ154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM154" t="n">
+        <v>3566</v>
+      </c>
+      <c r="AN154" t="n">
+        <v>14.55412226584408</v>
+      </c>
+      <c r="AO154" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ154" t="n">
         <v>0</v>
       </c>
     </row>
@@ -18165,6 +21413,27 @@
       <c r="AJ155" t="n">
         <v>0</v>
       </c>
+      <c r="AK155" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM155" t="n">
+        <v>3221</v>
+      </c>
+      <c r="AN155" t="n">
+        <v>9.686432784849426</v>
+      </c>
+      <c r="AO155" t="n">
+        <v>11</v>
+      </c>
+      <c r="AP155" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ155" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -18196,7 +21465,7 @@
         <v>54</v>
       </c>
       <c r="I156" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J156" t="n">
         <v>18</v>
@@ -18208,7 +21477,7 @@
         <v>19</v>
       </c>
       <c r="M156" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="N156" t="n">
         <v>9</v>
@@ -18217,7 +21486,7 @@
         <v>11</v>
       </c>
       <c r="P156" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Q156" t="n">
         <v>7</v>
@@ -18226,7 +21495,7 @@
         <v>21</v>
       </c>
       <c r="S156" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="T156" t="n">
         <v>9</v>
@@ -18277,6 +21546,27 @@
         <v>0</v>
       </c>
       <c r="AJ156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM156" t="n">
+        <v>3056</v>
+      </c>
+      <c r="AN156" t="n">
+        <v>22.02225130890052</v>
+      </c>
+      <c r="AO156" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ156" t="n">
         <v>0</v>
       </c>
     </row>
@@ -18310,7 +21600,7 @@
         <v>41</v>
       </c>
       <c r="I157" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J157" t="n">
         <v>16</v>
@@ -18340,7 +21630,7 @@
         <v>21</v>
       </c>
       <c r="S157" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="T157" t="n">
         <v>2</v>
@@ -18352,7 +21642,7 @@
         <v>1</v>
       </c>
       <c r="W157" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X157" t="n">
         <v>8</v>
@@ -18391,6 +21681,27 @@
         <v>2</v>
       </c>
       <c r="AJ157" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK157" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL157" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM157" t="n">
+        <v>3376</v>
+      </c>
+      <c r="AN157" t="n">
+        <v>13.71445497630332</v>
+      </c>
+      <c r="AO157" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP157" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ157" t="n">
         <v>1</v>
       </c>
     </row>
